--- a/data/b2_centro/B2 Centro 02-2026.xlsx
+++ b/data/b2_centro/B2 Centro 02-2026.xlsx
@@ -4501,43 +4501,43 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>670.74</v>
+        <v>677.3099999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>4358.69</v>
+        <v>78311.71000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46058</v>
+        <v>46061</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>79412.14999999999</v>
+        <v>3344.17</v>
       </c>
     </row>
     <row r="5">
@@ -4555,25 +4555,25 @@
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>5384.87</v>
+        <v>5658.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Aluguel do imóvel</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>38000</v>
+        <v>2002.64</v>
       </c>
     </row>
     <row r="7">
@@ -4582,52 +4582,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Aluguel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Aluguel do imóvel</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>4300</v>
+        <v>38000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>2062.35</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46067</v>
+        <v>46065</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1345.02</v>
+        <v>1932.8</v>
       </c>
     </row>
     <row r="10">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>13974.53</v>
+        <v>13064.5</v>
       </c>
     </row>
     <row r="11">
@@ -4654,16 +4654,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>4662.24</v>
+        <v>2519.78</v>
       </c>
     </row>
     <row r="12">
@@ -4672,39 +4672,39 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>5587.97</v>
+        <v>4531.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46070</v>
+        <v>46068</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Troca de filtros das bombas</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>2235.07</v>
+        <v>5530.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46071</v>
+        <v>46070</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
@@ -4713,11 +4713,11 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1376.21</v>
+        <v>1946.06</v>
       </c>
     </row>
     <row r="15">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>27492.61</v>
+        <v>27675.85</v>
       </c>
     </row>
     <row r="16">
@@ -4753,12 +4753,12 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>5809.41</v>
+        <v>5244.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -4767,11 +4767,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>2209.11</v>
+        <v>2369.63</v>
       </c>
     </row>
     <row r="18">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>5025.3</v>
+        <v>4933.5</v>
       </c>
     </row>
   </sheetData>
